--- a/resources/etsy/files/etsy-int-breakeven-traffic.xlsx
+++ b/resources/etsy/files/etsy-int-breakeven-traffic.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -500,7 +500,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -549,7 +548,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -598,7 +596,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -610,7 +607,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -688,7 +684,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>

--- a/resources/etsy/files/etsy-int-breakeven-traffic.xlsx
+++ b/resources/etsy/files/etsy-int-breakeven-traffic.xlsx
@@ -694,7 +694,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
